--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.26742814297556</v>
+        <v>5.730957073233529</v>
       </c>
       <c r="D2" t="n">
-        <v>33.76228107349878</v>
+        <v>5.486370674443553</v>
       </c>
       <c r="E2" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F2" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.87716717829593</v>
+        <v>5.505039666473088</v>
       </c>
       <c r="D3" t="n">
-        <v>34.99900509309661</v>
+        <v>5.687338327628199</v>
       </c>
       <c r="E3" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F3" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.13242059466667</v>
+        <v>7.009018346633334</v>
       </c>
       <c r="D4" t="n">
-        <v>41.0122263144637</v>
+        <v>6.664486776100352</v>
       </c>
       <c r="E4" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F4" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.89942028972799</v>
+        <v>3.558655797080798</v>
       </c>
       <c r="D5" t="n">
-        <v>21.61537320266279</v>
+        <v>3.512498145432704</v>
       </c>
       <c r="E5" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F5" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.38700106999539</v>
+        <v>11.11288767387425</v>
       </c>
       <c r="D6" t="n">
-        <v>66.25674395955456</v>
+        <v>10.76672089342762</v>
       </c>
       <c r="E6" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F6" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.21541721694795</v>
+        <v>5.560005297754042</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75078978101252</v>
+        <v>5.809503339414535</v>
       </c>
       <c r="E7" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F7" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.14589553897751</v>
+        <v>4.248708025083846</v>
       </c>
       <c r="D8" t="n">
-        <v>27.4841477092879</v>
+        <v>4.466174002759283</v>
       </c>
       <c r="E8" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F8" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.81718052155242</v>
+        <v>4.357791834752268</v>
       </c>
       <c r="D9" t="n">
-        <v>28.58404221164473</v>
+        <v>4.644906859392269</v>
       </c>
       <c r="E9" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F9" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.7459919200134</v>
+        <v>5.321223687002179</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60467984493293</v>
+        <v>4.973260474801601</v>
       </c>
       <c r="E10" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F10" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.10562772967371</v>
+        <v>6.679664506071978</v>
       </c>
       <c r="D11" t="n">
-        <v>43.20476989276977</v>
+        <v>7.020775107575088</v>
       </c>
       <c r="E11" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F11" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.51037832243968</v>
+        <v>5.120436477396449</v>
       </c>
       <c r="D12" t="n">
-        <v>29.79159053026259</v>
+        <v>4.84113346116767</v>
       </c>
       <c r="E12" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F12" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.8807058787974</v>
+        <v>7.455614705304578</v>
       </c>
       <c r="D13" t="n">
-        <v>48.02042153002429</v>
+        <v>7.803318498628948</v>
       </c>
       <c r="E13" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F13" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>53.47586624396181</v>
+        <v>8.689828264643795</v>
       </c>
       <c r="D14" t="n">
-        <v>55.60125362505335</v>
+        <v>9.035203714071169</v>
       </c>
       <c r="E14" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F14" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.21640524091831</v>
+        <v>3.285165851649225</v>
       </c>
       <c r="D15" t="n">
-        <v>22.45112880341231</v>
+        <v>3.6483084305545</v>
       </c>
       <c r="E15" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F15" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.1819433618994</v>
+        <v>6.854565796308653</v>
       </c>
       <c r="D16" t="n">
-        <v>42.6611064412719</v>
+        <v>6.932429796706685</v>
       </c>
       <c r="E16" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F16" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.18414092591647</v>
+        <v>4.742422900461427</v>
       </c>
       <c r="D17" t="n">
-        <v>31.55397974842601</v>
+        <v>5.127521709119226</v>
       </c>
       <c r="E17" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F17" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>12.7791997957706</v>
+        <v>2.076619966812723</v>
       </c>
       <c r="D18" t="n">
-        <v>16.42045634826281</v>
+        <v>2.668324156592707</v>
       </c>
       <c r="E18" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F18" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>11.23556506898789</v>
+        <v>1.825779323710532</v>
       </c>
       <c r="D19" t="n">
-        <v>2.852873794770614</v>
+        <v>0.4635919916502248</v>
       </c>
       <c r="E19" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F19" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.62064947307741</v>
+        <v>2.700855539375079</v>
       </c>
       <c r="D20" t="n">
-        <v>13.3842776752759</v>
+        <v>2.174945122232334</v>
       </c>
       <c r="E20" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F20" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>20.65588428616545</v>
+        <v>3.356581196501885</v>
       </c>
       <c r="D21" t="n">
-        <v>21.33641285868931</v>
+        <v>3.467167089537013</v>
       </c>
       <c r="E21" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F21" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>21.46555689615773</v>
+        <v>3.488152995625631</v>
       </c>
       <c r="D22" t="n">
-        <v>21.85846375235499</v>
+        <v>3.552000359757686</v>
       </c>
       <c r="E22" t="n">
-        <v>13.61819021916747</v>
+        <v>2.212955910614714</v>
       </c>
       <c r="F22" t="n">
-        <v>14.18737092722945</v>
+        <v>2.305447775674786</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
